--- a/output/pdf_financials_xlsx/GRHK.xlsx
+++ b/output/pdf_financials_xlsx/GRHK.xlsx
@@ -612,10 +612,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.218219</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.051781</v>
       </c>
     </row>
     <row r="13">
@@ -864,10 +864,10 @@
         <v>-1.52512</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-3.357805</v>
+        <v>-3.576024</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.502509</v>
+        <v>-1.55429</v>
       </c>
     </row>
     <row r="28">
@@ -896,10 +896,10 @@
         <v>-1.52512</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-3.357805</v>
+        <v>-3.576024</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.502509</v>
+        <v>-1.55429</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>3.579462</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.116291</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.232934</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>3.579462</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.116291</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.232934</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.584537</v>
+        <v>0.005075</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.273135</v>
+        <v>0.156844</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.267659</v>
+        <v>0.034725</v>
       </c>
     </row>
     <row r="49">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -4040,7 +4040,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">

--- a/output/pdf_financials_xlsx/GRHK.xlsx
+++ b/output/pdf_financials_xlsx/GRHK.xlsx
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.004899</v>
       </c>
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.020607</v>
       </c>
     </row>
     <row r="112">
@@ -2597,13 +2597,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.004899</v>
       </c>
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.020607</v>
       </c>
     </row>
     <row r="135">
@@ -2613,13 +2613,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.9782110000000001</v>
+        <v>-0.98311</v>
       </c>
       <c r="C135" s="3" t="n">
         <v>-0.763171</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>0.03725</v>
+        <v>0.016643</v>
       </c>
     </row>
   </sheetData>
@@ -3602,7 +3602,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E31" s="5" t="n">
         <v>-0.004899</v>
       </c>
